--- a/Compititor's_Price/IKO_Prices/IKO_Prices_02-01-2026.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_02-01-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="64">
   <si>
     <t>SKU</t>
   </si>
@@ -206,48 +206,6 @@
   </si>
   <si>
     <t>POA</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/25mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/30mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/40mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/50mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/60mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/70mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/75mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/80mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/90mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/100mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/110mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/120mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/140mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://materialsmarket.com/products/150mm-iko-enertherm-alu-pir-insulation-board-2400mm-x-1200mm</t>
   </si>
 </sst>
 </file>
@@ -666,7 +624,7 @@
         <v>59</v>
       </c>
       <c r="I2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J2" t="s">
         <v>59</v>
@@ -698,7 +656,7 @@
         <v>59</v>
       </c>
       <c r="I3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J3" t="s">
         <v>63</v>
@@ -730,7 +688,7 @@
         <v>59</v>
       </c>
       <c r="I4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J4" t="s">
         <v>63</v>
@@ -762,7 +720,7 @@
         <v>59</v>
       </c>
       <c r="I5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J5" t="s">
         <v>63</v>
@@ -794,7 +752,7 @@
         <v>59</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="J6" t="s">
         <v>63</v>
@@ -826,7 +784,7 @@
         <v>59</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J7" t="s">
         <v>63</v>
@@ -858,7 +816,7 @@
         <v>59</v>
       </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J8" t="s">
         <v>59</v>
@@ -890,7 +848,7 @@
         <v>59</v>
       </c>
       <c r="I9" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="J9" t="s">
         <v>63</v>
@@ -922,7 +880,7 @@
         <v>59</v>
       </c>
       <c r="I10" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J10" t="s">
         <v>63</v>
@@ -954,7 +912,7 @@
         <v>59</v>
       </c>
       <c r="I11" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J11" t="s">
         <v>63</v>
@@ -986,7 +944,7 @@
         <v>59</v>
       </c>
       <c r="I12" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="J12" t="s">
         <v>63</v>
@@ -1018,7 +976,7 @@
         <v>59</v>
       </c>
       <c r="I13" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="J13" t="s">
         <v>63</v>
@@ -1050,7 +1008,7 @@
         <v>59</v>
       </c>
       <c r="I14" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="J14" t="s">
         <v>63</v>
@@ -1082,7 +1040,7 @@
         <v>59</v>
       </c>
       <c r="I15" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="J15" t="s">
         <v>63</v>

--- a/Compititor's_Price/IKO_Prices/IKO_Prices_02-01-2026.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_02-01-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="65">
   <si>
     <t>SKU</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>Materials Market</t>
+  </si>
+  <si>
+    <t>Insulation Wholesale</t>
   </si>
   <si>
     <t>Insulation Shop</t>
@@ -563,10 +566,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -597,453 +600,498 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" t="s">
+        <v>64</v>
+      </c>
+      <c r="K14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B15" t="s">
         <v>38</v>
       </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C15" t="s">
         <v>52</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" t="s">
         <v>63</v>
       </c>
-      <c r="H2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" t="s">
-        <v>63</v>
-      </c>
-      <c r="J5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I10" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H11" t="s">
-        <v>59</v>
-      </c>
-      <c r="I11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" t="s">
-        <v>59</v>
-      </c>
-      <c r="I13" t="s">
-        <v>63</v>
-      </c>
-      <c r="J13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H14" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J15" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="K15" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
